--- a/4063.T_report.xlsx
+++ b/4063.T_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,58 +449,668 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>手数料込み利益率(%)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>手数料(円)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>決済後資産(円)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>保有日数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>決済理由</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>バックテスト結果</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="I2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-03-07</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2023-03-31</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3785.96</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4026.24</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2063</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1061402</v>
+      </c>
+      <c r="J2" t="n">
+        <v>24</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>総取引回数</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
+      <c r="M2" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="3">
-      <c r="I3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2023-04-03</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2023-04-06</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3946.53</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3712.61</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-5.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2060</v>
+      </c>
+      <c r="I3" t="n">
+        <v>996431</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>勝率</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="I4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2023-06-09</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4270.22</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4567.78</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2062</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1063801</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>総利益率</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>-2.80%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="I5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4464.62</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4301.24</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-3.66</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-3.86</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2089</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1022784</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>平均保有日数</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.0日</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>10.1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4441.03</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4294.65</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-3.49</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2012</v>
+      </c>
+      <c r="I6" t="n">
+        <v>987061</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>最終資産</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>971973</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2023-12-27</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5215.62</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5535.7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2035</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1045602</v>
+      </c>
+      <c r="J7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>手数料込み利益</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>-28027</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2024-02-15</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5857.91</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6271</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2165</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1117172</v>
+      </c>
+      <c r="J8" t="n">
+        <v>15</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>総手数料</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>29096</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2024-04-02</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6272.11</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6109.12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2205</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1085935</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4649.91</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4436.89</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-4.58</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2122</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1034066</v>
+      </c>
+      <c r="J10" t="n">
+        <v>28</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4906.23</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5391.61</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2170</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1134198</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5407.37</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4818.18</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-11.09</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2145</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1008472</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6178.43</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5912.55</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1974</v>
+      </c>
+      <c r="I13" t="n">
+        <v>963100</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6051.41</v>
+      </c>
+      <c r="E14" t="n">
+        <v>6468.15</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1993</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1027433</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>7487.48</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7097.9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2001</v>
+      </c>
+      <c r="I15" t="n">
+        <v>971973</v>
+      </c>
+      <c r="J15" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
         </is>
       </c>
     </row>

--- a/4063.T_report.xlsx
+++ b/4063.T_report.xlsx
@@ -759,7 +759,7 @@
         <v>2035</v>
       </c>
       <c r="I7" t="n">
-        <v>1045602</v>
+        <v>1045603</v>
       </c>
       <c r="J7" t="n">
         <v>9</v>
